--- a/data/trans_dic/P02E$otras-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,33; 25,31</t>
+          <t>11,36; 25,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 14,6</t>
+          <t>4,67; 14,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 15,4</t>
+          <t>4,0; 15,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 13,4</t>
+          <t>3,46; 13,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 10,4</t>
+          <t>2,44; 9,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 18,4</t>
+          <t>7,26; 18,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,44; 17,13</t>
+          <t>8,34; 17,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 10,38</t>
+          <t>4,44; 10,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 14,88</t>
+          <t>7,0; 15,15</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 15,91</t>
+          <t>2,49; 16,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 11,09</t>
+          <t>2,97; 11,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 13,11</t>
+          <t>3,62; 13,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 9,8</t>
+          <t>2,7; 10,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,76</t>
+          <t>2,45; 8,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,77; 19,7</t>
+          <t>8,87; 20,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 10,51</t>
+          <t>3,46; 10,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 8,28</t>
+          <t>3,28; 8,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 15,29</t>
+          <t>7,52; 15,64</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 10,05</t>
+          <t>2,35; 10,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 9,31</t>
+          <t>2,9; 9,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 20,35</t>
+          <t>4,75; 20,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 16,38</t>
+          <t>4,0; 16,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,7</t>
+          <t>0,0; 10,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 11,79</t>
+          <t>4,11; 12,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 9,55</t>
+          <t>4,15; 9,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,03</t>
+          <t>0,47; 4,22</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 10,59</t>
+          <t>3,96; 10,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,75</t>
+          <t>2,82; 7,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,82</t>
+          <t>2,44; 7,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 11,45</t>
+          <t>4,43; 10,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,31</t>
+          <t>2,78; 7,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 15,27</t>
+          <t>8,45; 15,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,65</t>
+          <t>5,07; 10,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,35</t>
+          <t>3,42; 6,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 11,02</t>
+          <t>6,07; 10,91</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 13,31</t>
+          <t>1,59; 13,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,72</t>
+          <t>0,77; 7,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 11,74</t>
+          <t>3,61; 12,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,93</t>
+          <t>2,89; 10,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 10,0</t>
+          <t>4,7; 10,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 11,35</t>
+          <t>4,4; 11,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 9,02</t>
+          <t>3,12; 9,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,37</t>
+          <t>3,9; 8,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 10,4</t>
+          <t>5,04; 10,46</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,94</t>
+          <t>0,0; 25,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,43</t>
+          <t>1,66; 6,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,26</t>
+          <t>1,35; 5,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,23</t>
+          <t>2,34; 9,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,39</t>
+          <t>1,64; 6,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,31</t>
+          <t>1,14; 5,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 8,7</t>
+          <t>2,64; 9,35</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,39</t>
+          <t>6,35; 10,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,81</t>
+          <t>3,87; 6,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,74; 6,89</t>
+          <t>3,65; 6,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 7,77</t>
+          <t>4,77; 7,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,47</t>
+          <t>4,25; 6,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,59; 11,23</t>
+          <t>7,68; 11,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,7; 8,39</t>
+          <t>5,66; 8,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 6,2</t>
+          <t>4,42; 6,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,39; 8,91</t>
+          <t>6,56; 9,07</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12922; 28877</t>
+          <t>12955; 29425</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7026; 22020</t>
+          <t>7045; 22182</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3560; 14919</t>
+          <t>3877; 14690</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3693; 14230</t>
+          <t>3676; 13903</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4073; 17020</t>
+          <t>3991; 16116</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9681; 26277</t>
+          <t>10369; 26056</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18590; 37718</t>
+          <t>18367; 38497</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13512; 32651</t>
+          <t>13962; 32875</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16629; 35676</t>
+          <t>16781; 36318</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1924; 13560</t>
+          <t>2124; 13743</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3845; 17142</t>
+          <t>4588; 17168</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3536; 14049</t>
+          <t>3881; 14849</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3955; 13992</t>
+          <t>3851; 15100</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4900; 17348</t>
+          <t>4844; 16614</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13808; 30995</t>
+          <t>13962; 32068</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8074; 23958</t>
+          <t>7881; 24020</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11462; 29179</t>
+          <t>11558; 29088</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19203; 40452</t>
+          <t>19894; 41358</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2656; 12124</t>
+          <t>2831; 12512</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5556; 18097</t>
+          <t>5645; 18617</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4761</t>
+          <t>0; 5519</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3245; 13714</t>
+          <t>3202; 13582</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4376; 17915</t>
+          <t>4377; 17509</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5821</t>
+          <t>0; 5936</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7890; 22175</t>
+          <t>7728; 22828</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12732; 29009</t>
+          <t>12597; 29648</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>921; 7843</t>
+          <t>922; 8209</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8887; 24757</t>
+          <t>9264; 25509</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9088; 26468</t>
+          <t>9624; 24882</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6690; 20016</t>
+          <t>6240; 19816</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11027; 28551</t>
+          <t>11036; 27044</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12017; 29150</t>
+          <t>11069; 28369</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25079; 47213</t>
+          <t>26106; 47801</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25042; 46627</t>
+          <t>24499; 48286</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24599; 46976</t>
+          <t>25282; 47874</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35579; 62297</t>
+          <t>34303; 61655</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>971; 8298</t>
+          <t>990; 8426</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1045; 9092</t>
+          <t>1038; 10440</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4274; 15974</t>
+          <t>4910; 16446</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5957; 18829</t>
+          <t>5473; 19056</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16159; 35775</t>
+          <t>16815; 35995</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11387; 28310</t>
+          <t>10967; 29022</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8094; 22738</t>
+          <t>7871; 23329</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19622; 41246</t>
+          <t>19239; 40054</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18276; 40090</t>
+          <t>19435; 40308</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1906</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1698</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5018</t>
+          <t>0; 4870</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4251; 16043</t>
+          <t>4145; 16841</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3903; 15070</t>
+          <t>3861; 14721</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5086; 17943</t>
+          <t>4548; 17975</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4134; 16606</t>
+          <t>4251; 16778</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3999; 15643</t>
+          <t>3365; 14858</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5606; 18590</t>
+          <t>5639; 19985</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>38959; 65075</t>
+          <t>39746; 66857</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>37619; 67032</t>
+          <t>38149; 66076</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28243; 52036</t>
+          <t>27560; 52568</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47208; 78035</t>
+          <t>47911; 77237</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>65643; 98002</t>
+          <t>64336; 100056</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>84044; 124391</t>
+          <t>85016; 127345</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93030; 136842</t>
+          <t>92246; 134516</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>111067; 155018</t>
+          <t>110353; 156652</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>119099; 166074</t>
+          <t>122304; 168922</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$otras-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,36; 25,79</t>
+          <t>11,21; 24,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 14,71</t>
+          <t>4,68; 14,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 15,17</t>
+          <t>3,89; 15,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 13,1</t>
+          <t>3,33; 13,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,85</t>
+          <t>2,52; 11,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 18,24</t>
+          <t>7,09; 18,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,34; 17,48</t>
+          <t>8,45; 16,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 10,45</t>
+          <t>4,71; 10,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 15,15</t>
+          <t>6,78; 15,16</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 16,13</t>
+          <t>2,37; 15,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 11,11</t>
+          <t>2,63; 11,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 13,86</t>
+          <t>3,58; 13,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 10,58</t>
+          <t>2,76; 11,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,39</t>
+          <t>2,44; 8,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 20,38</t>
+          <t>8,27; 19,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 10,54</t>
+          <t>3,28; 9,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,25</t>
+          <t>3,17; 8,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 15,64</t>
+          <t>7,69; 15,36</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 10,37</t>
+          <t>2,3; 10,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,58</t>
+          <t>2,67; 9,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 20,16</t>
+          <t>4,68; 21,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 16,01</t>
+          <t>3,98; 16,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,91</t>
+          <t>0,0; 10,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 12,14</t>
+          <t>4,45; 11,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 9,76</t>
+          <t>3,9; 10,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,22</t>
+          <t>0,47; 4,06</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 10,91</t>
+          <t>4,04; 10,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,28</t>
+          <t>2,86; 7,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,74</t>
+          <t>2,63; 8,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 10,85</t>
+          <t>4,63; 11,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,12</t>
+          <t>3,04; 7,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 15,46</t>
+          <t>8,21; 15,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 10,0</t>
+          <t>5,04; 9,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,47</t>
+          <t>3,35; 6,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 10,91</t>
+          <t>6,35; 11,05</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 13,51</t>
+          <t>1,58; 13,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,72</t>
+          <t>0,77; 6,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 12,09</t>
+          <t>3,07; 11,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 10,05</t>
+          <t>2,74; 9,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,7; 10,06</t>
+          <t>4,75; 10,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 11,63</t>
+          <t>4,46; 11,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,26</t>
+          <t>3,26; 9,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,12</t>
+          <t>3,94; 7,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 10,46</t>
+          <t>4,75; 10,15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,18</t>
+          <t>0,0; 33,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,75</t>
+          <t>1,67; 6,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,14</t>
+          <t>1,41; 5,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 9,25</t>
+          <t>2,59; 9,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,46</t>
+          <t>1,68; 6,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,04</t>
+          <t>1,36; 5,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 9,35</t>
+          <t>2,54; 8,97</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,68</t>
+          <t>6,14; 10,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,71</t>
+          <t>3,9; 6,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,65; 6,96</t>
+          <t>3,73; 6,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,69</t>
+          <t>4,74; 7,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,61</t>
+          <t>4,22; 6,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,68; 11,5</t>
+          <t>7,75; 11,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,25</t>
+          <t>5,74; 8,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,27</t>
+          <t>4,44; 6,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 9,07</t>
+          <t>6,51; 9,06</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12955; 29425</t>
+          <t>12790; 28481</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7045; 22182</t>
+          <t>7054; 21761</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3877; 14690</t>
+          <t>3770; 14993</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3676; 13903</t>
+          <t>3537; 14007</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3991; 16116</t>
+          <t>4119; 18346</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10369; 26056</t>
+          <t>10126; 26460</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18367; 38497</t>
+          <t>18600; 37283</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13962; 32875</t>
+          <t>14811; 33294</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16781; 36318</t>
+          <t>16249; 36334</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2124; 13743</t>
+          <t>2020; 13085</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4588; 17168</t>
+          <t>4059; 17627</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3881; 14849</t>
+          <t>3832; 14002</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3851; 15100</t>
+          <t>3933; 15840</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4844; 16614</t>
+          <t>4838; 17078</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13962; 32068</t>
+          <t>13007; 30985</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7881; 24020</t>
+          <t>7471; 22552</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11558; 29088</t>
+          <t>11164; 28519</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19894; 41358</t>
+          <t>20329; 40625</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2831; 12512</t>
+          <t>2777; 12911</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5645; 18617</t>
+          <t>5182; 18240</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5519</t>
+          <t>0; 4168</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3202; 13582</t>
+          <t>3151; 14542</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4377; 17509</t>
+          <t>4356; 17913</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5936</t>
+          <t>0; 5738</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7728; 22828</t>
+          <t>8376; 22253</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12597; 29648</t>
+          <t>11842; 30536</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>922; 8209</t>
+          <t>911; 7900</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9264; 25509</t>
+          <t>9443; 24376</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9624; 24882</t>
+          <t>9763; 25340</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6240; 19816</t>
+          <t>6736; 21094</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11036; 27044</t>
+          <t>11555; 28716</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11069; 28369</t>
+          <t>12102; 28798</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26106; 47801</t>
+          <t>25393; 47489</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24499; 48286</t>
+          <t>24357; 47604</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25282; 47874</t>
+          <t>24817; 48099</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34303; 61655</t>
+          <t>35916; 62459</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>990; 8426</t>
+          <t>985; 8342</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1038; 10440</t>
+          <t>1038; 9439</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4910; 16446</t>
+          <t>4183; 16177</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5473; 19056</t>
+          <t>5201; 18001</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16815; 35995</t>
+          <t>17007; 36359</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10967; 29022</t>
+          <t>11117; 27805</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7871; 23329</t>
+          <t>8221; 24098</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19239; 40054</t>
+          <t>19414; 39096</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19435; 40308</t>
+          <t>18303; 39131</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4870</t>
+          <t>0; 6497</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4145; 16841</t>
+          <t>4176; 16545</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3861; 14721</t>
+          <t>4030; 15702</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4548; 17975</t>
+          <t>5037; 18663</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4251; 16778</t>
+          <t>4363; 16628</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3365; 14858</t>
+          <t>4006; 15606</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5639; 19985</t>
+          <t>5424; 19176</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>39746; 66857</t>
+          <t>38436; 66471</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>38149; 66076</t>
+          <t>38440; 67796</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27560; 52568</t>
+          <t>28205; 52190</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47911; 77237</t>
+          <t>47661; 78641</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>64336; 100056</t>
+          <t>63951; 98925</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85016; 127345</t>
+          <t>85873; 124310</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92246; 134516</t>
+          <t>93666; 136102</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>110353; 156652</t>
+          <t>110968; 154503</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>122304; 168922</t>
+          <t>121199; 168853</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$otras-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
